--- a/Result/profitability/8240.xlsx
+++ b/Result/profitability/8240.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.66</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4775</v>
+        <v>0.35875</v>
       </c>
       <c r="N2" t="n">
-        <v>14.305</v>
+        <v>14.17875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>0.31625</v>
+        <v>0.3925</v>
       </c>
       <c r="N3" t="n">
-        <v>13.95375</v>
+        <v>13.91375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.97</v>
       </c>
       <c r="M4" t="n">
-        <v>0.41625</v>
+        <v>0.41875</v>
       </c>
       <c r="N4" t="n">
-        <v>14.00625</v>
+        <v>13.62375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>0.285</v>
+        <v>0.35125</v>
       </c>
       <c r="N5" t="n">
-        <v>13.085</v>
+        <v>12.96</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.58</v>
       </c>
       <c r="M6" t="n">
-        <v>0.18125</v>
+        <v>0.2125</v>
       </c>
       <c r="N6" t="n">
-        <v>11.99</v>
+        <v>11.79</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>0.28</v>
+        <v>0.2975</v>
       </c>
       <c r="N7" t="n">
-        <v>11.865</v>
+        <v>11.66375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3825</v>
+        <v>0.43</v>
       </c>
       <c r="N8" t="n">
-        <v>11.9875</v>
+        <v>11.84125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>1.09</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6849999999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>12.3375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8240</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1640</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1417</v>
+      </c>
+      <c r="E75" t="n">
+        <v>223</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="G75" t="n">
+        <v>22</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>65</v>
+      </c>
+      <c r="J75" t="n">
+        <v>87</v>
+      </c>
+      <c r="K75" t="n">
+        <v>78</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6575</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.83125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07916102841677941</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.06844626967830258</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
